--- a/artfynd/A 31336-2025 artfynd.xlsx
+++ b/artfynd/A 31336-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126265528</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126265538</v>
       </c>
       <c r="B3" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126265526</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31336-2025 artfynd.xlsx
+++ b/artfynd/A 31336-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126265528</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126265538</v>
       </c>
       <c r="B3" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126265526</v>
       </c>
       <c r="B4" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31336-2025 artfynd.xlsx
+++ b/artfynd/A 31336-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>126265528</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -779,11 +779,11 @@
         <v>126265538</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -878,112 +878,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>126265526</v>
-      </c>
-      <c r="B4" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Gangsberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>473694</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6801772</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>högstubbe</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Bengt Oldhammer</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Bengt Oldhammer, Peter Turander</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31336-2025 artfynd.xlsx
+++ b/artfynd/A 31336-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126265528</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,8 +888,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126265538</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>